--- a/5°anno/GPOI/es_pag8.xlsx
+++ b/5°anno/GPOI/es_pag8.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Desktop\FILE SCUOLA\Cartella Repository\repository_generale\5°anno\GPOI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{152DC3D0-48AC-47DA-90D9-B183CDE31634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86495900-5E77-42A2-A927-2759EA53E060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B2A40651-5BF7-439F-A35A-CFCF6A0A3041}"/>
   </bookViews>
@@ -39,13 +39,46 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t xml:space="preserve">pe = 100 - 2q </t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>pe</t>
+  </si>
+  <si>
+    <t>pi</t>
+  </si>
+  <si>
+    <t>pi = pe + 20pe / 100</t>
+  </si>
+  <si>
+    <t>Reddito = 100</t>
+  </si>
+  <si>
+    <t>Reddito = 120</t>
+  </si>
+  <si>
+    <t>pi = 120 - 2q</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -73,8 +106,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -90,6 +124,1250 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="it-IT"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="it-IT"/>
+              <a:t>Spostamento</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="it-IT" baseline="0"/>
+              <a:t> domanda arance</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="it-IT" baseline="0"/>
+              <a:t>(estate - inverno)</a:t>
+            </a:r>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="it-IT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>PrezzoEstivo</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Foglio1!$A$2:$A$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Foglio1!$B$2:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F4A8-4EFC-8599-E1138FEF16E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>PrezzoInvernale</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Foglio1!$A$4:$A$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Foglio1!$C$4:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F4A8-4EFC-8599-E1138FEF16E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="983556176"/>
+        <c:axId val="985848432"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="983556176"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>prezzo</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="985848432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="985848432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>quantità</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="983556176"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="it-IT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="it-IT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Grafico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D332F876-351F-655F-25D7-7D5C14F1A53D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -409,17 +1687,185 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3532729-CEDF-491A-A710-414283DF0114}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.109375" customWidth="1"/>
     <col min="8" max="8" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <f xml:space="preserve"> 100 - 2 *A2</f>
+        <v>90</v>
+      </c>
+      <c r="E2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B11" si="0" xml:space="preserve"> 100 - 2 *A3</f>
+        <v>80</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C3:C13" si="1" xml:space="preserve"> 120 - 2*A4</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>30</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>35</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>40</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>45</v>
+      </c>
+      <c r="B10">
+        <f xml:space="preserve"> 100 - 2 *A10</f>
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>50</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>55</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>60</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/5°anno/GPOI/es_pag8.xlsx
+++ b/5°anno/GPOI/es_pag8.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Desktop\FILE SCUOLA\Cartella Repository\repository_generale\5°anno\GPOI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Desktop\repository_generale\5°anno\GPOI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86495900-5E77-42A2-A927-2759EA53E060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D7DE4E-5577-4C61-B79E-22E822CF6AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B2A40651-5BF7-439F-A35A-CFCF6A0A3041}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,12 +23,8 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">pe = 100 - 2q </t>
   </si>
@@ -64,12 +60,30 @@
   <si>
     <t>pi = 120 - 2q</t>
   </si>
+  <si>
+    <t>(q - q1) / (q2 - q1) = (p - p1) / (p2 - p1)</t>
+  </si>
+  <si>
+    <t>(q - 10) / (40 - 10) = (p - 80) / (20 - 80)</t>
+  </si>
+  <si>
+    <t>(q - 10) / 30 = (p - 80) / (-60)</t>
+  </si>
+  <si>
+    <t>p - 80 = (q - 10) * (-2)</t>
+  </si>
+  <si>
+    <t>p = 100 - 2q</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,7 +184,17 @@
           </a:p>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr lang="it-IT" baseline="0"/>
@@ -731,7 +755,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -739,6 +762,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1687,17 +1711,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3532729-CEDF-491A-A710-414283DF0114}">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.09765625" customWidth="1"/>
+    <col min="8" max="8" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1714,7 +1738,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>5</v>
       </c>
@@ -1726,7 +1750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>10</v>
       </c>
@@ -1741,7 +1765,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>15</v>
       </c>
@@ -1750,11 +1774,11 @@
         <v>70</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C3:C13" si="1" xml:space="preserve"> 120 - 2*A4</f>
+        <f xml:space="preserve"> 120 - 2*A4</f>
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>20</v>
       </c>
@@ -1763,11 +1787,11 @@
         <v>60</v>
       </c>
       <c r="C5">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C4:C13" si="1" xml:space="preserve"> 120 - 2*A5</f>
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>25</v>
       </c>
@@ -1780,7 +1804,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>30</v>
       </c>
@@ -1793,7 +1817,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>35</v>
       </c>
@@ -1806,7 +1830,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>40</v>
       </c>
@@ -1819,7 +1843,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>45</v>
       </c>
@@ -1832,7 +1856,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>50</v>
       </c>
@@ -1845,7 +1869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>55</v>
       </c>
@@ -1854,13 +1878,43 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>60</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5" ht="14.4">
+      <c r="E21" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="5:5">
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="5:5">
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="5:5">
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="5:5">
+      <c r="E26" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/5°anno/GPOI/es_pag8.xlsx
+++ b/5°anno/GPOI/es_pag8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Desktop\repository_generale\5°anno\GPOI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D7DE4E-5577-4C61-B79E-22E822CF6AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35088BA1-517C-43F1-BDFB-269C0769B0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B2A40651-5BF7-439F-A35A-CFCF6A0A3041}"/>
   </bookViews>
@@ -1721,7 +1721,7 @@
     <col min="10" max="10" width="12.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="14.4">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>60</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C4:C13" si="1" xml:space="preserve"> 120 - 2*A5</f>
+        <f t="shared" ref="C5:C13" si="1" xml:space="preserve"> 120 - 2*A5</f>
         <v>80</v>
       </c>
     </row>

--- a/5°anno/GPOI/es_pag8.xlsx
+++ b/5°anno/GPOI/es_pag8.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Desktop\repository_generale\5°anno\GPOI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35088BA1-517C-43F1-BDFB-269C0769B0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E354D703-410C-4D2C-A548-C356252F98EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B2A40651-5BF7-439F-A35A-CFCF6A0A3041}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,8 +24,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -83,7 +88,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,17 +189,7 @@
           </a:p>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
               <a:rPr lang="it-IT" baseline="0"/>
@@ -522,7 +517,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="it-IT"/>
-                  <a:t>prezzo</a:t>
+                  <a:t>quantità</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -639,7 +634,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="it-IT"/>
-                  <a:t>quantità</a:t>
+                  <a:t>prezzo</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -755,6 +750,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -762,7 +758,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1712,16 +1707,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3532729-CEDF-491A-A710-414283DF0114}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="14.09765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.09765625" customWidth="1"/>
-    <col min="8" max="8" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1738,7 +1733,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5</v>
       </c>
@@ -1750,7 +1745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10</v>
       </c>
@@ -1765,7 +1760,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>15</v>
       </c>
@@ -1778,7 +1773,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>20</v>
       </c>
@@ -1791,7 +1786,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25</v>
       </c>
@@ -1804,7 +1799,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>30</v>
       </c>
@@ -1817,7 +1812,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>35</v>
       </c>
@@ -1830,7 +1825,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>40</v>
       </c>
@@ -1843,7 +1838,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>45</v>
       </c>
@@ -1856,7 +1851,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>50</v>
       </c>
@@ -1869,7 +1864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>55</v>
       </c>
@@ -1878,7 +1873,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>60</v>
       </c>
@@ -1887,32 +1882,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="5:5" ht="14.4">
+    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E21" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="5:5">
+    <row r="22" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E22" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="5:5">
+    <row r="23" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E23" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="5:5">
+    <row r="24" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E24" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="5:5">
+    <row r="25" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E25" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="5:5">
+    <row r="26" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E26" t="s">
         <v>12</v>
       </c>

--- a/5°anno/GPOI/es_pag8.xlsx
+++ b/5°anno/GPOI/es_pag8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Desktop\repository_generale\5°anno\GPOI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E354D703-410C-4D2C-A548-C356252F98EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2F83F0-37B7-4C07-ADD8-837BCBD44FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B2A40651-5BF7-439F-A35A-CFCF6A0A3041}"/>
   </bookViews>
@@ -125,9 +125,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1358,8 +1359,8 @@
       <xdr:rowOff>179070</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>960120</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>179070</xdr:rowOff>
     </xdr:to>
@@ -1706,17 +1707,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3532729-CEDF-491A-A710-414283DF0114}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="14.109375" customWidth="1"/>
     <col min="10" max="10" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10</v>
       </c>
@@ -1759,8 +1759,9 @@
       <c r="F3" t="s">
         <v>7</v>
       </c>
+      <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>15</v>
       </c>
@@ -1773,7 +1774,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>20</v>
       </c>
@@ -1786,7 +1787,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25</v>
       </c>
@@ -1799,7 +1800,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>30</v>
       </c>
@@ -1812,7 +1813,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>35</v>
       </c>
@@ -1825,7 +1826,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>40</v>
       </c>
@@ -1838,7 +1839,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>45</v>
       </c>
@@ -1851,7 +1852,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>50</v>
       </c>
@@ -1864,7 +1865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>55</v>
       </c>
@@ -1873,7 +1874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>60</v>
       </c>
